--- a/Resultados Open Field/resultados OF.xlsx
+++ b/Resultados Open Field/resultados OF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thiago\tesis-pfc\Resultados Open Field\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5763A587-A5B5-4699-B721-3BE2F64044E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40E72EA-FB3C-4C9C-B56C-02BB23539F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="11" xr2:uid="{7160D138-BA09-422E-B688-42623F3FA4B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="17" activeTab="18" xr2:uid="{7160D138-BA09-422E-B688-42623F3FA4B8}"/>
   </bookViews>
   <sheets>
     <sheet name="distancia zona 1" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,18 @@
     <sheet name="dis total" sheetId="10" r:id="rId10"/>
     <sheet name="dist total 2wa" sheetId="11" r:id="rId11"/>
     <sheet name="mc dist total" sheetId="12" r:id="rId12"/>
+    <sheet name="Z1 +Z2 DIST" sheetId="13" r:id="rId13"/>
+    <sheet name="Z1 +Z2 DIST 2ANOVA" sheetId="14" r:id="rId14"/>
+    <sheet name="Z1+Z2 MPCOMP DIST" sheetId="15" r:id="rId15"/>
+    <sheet name="REARING TIME" sheetId="16" r:id="rId16"/>
+    <sheet name="REARING TIME 2WA" sheetId="17" r:id="rId17"/>
+    <sheet name="REARING TIME MPCPM" sheetId="18" r:id="rId18"/>
+    <sheet name="entries z1" sheetId="19" r:id="rId19"/>
+    <sheet name="z1 2wa" sheetId="20" r:id="rId20"/>
+    <sheet name="z1 mp comp" sheetId="21" r:id="rId21"/>
+    <sheet name="total zonas visitadas" sheetId="22" r:id="rId22"/>
+    <sheet name="Total zs visitadas 2wa" sheetId="23" r:id="rId23"/>
+    <sheet name="total zs mp comp" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="186">
   <si>
     <t>control</t>
   </si>
@@ -410,6 +422,204 @@
   </si>
   <si>
     <t>Predicted (LS) mean 2</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Stevia</t>
+  </si>
+  <si>
+    <t>Jóvenes</t>
+  </si>
+  <si>
+    <t>Adultos</t>
+  </si>
+  <si>
+    <t>Two-way ANOVA , distance zone 1+2</t>
+  </si>
+  <si>
+    <t>F (2, 69) = 5.049</t>
+  </si>
+  <si>
+    <t>P=0.0090</t>
+  </si>
+  <si>
+    <t>F (1, 69) = 3.152</t>
+  </si>
+  <si>
+    <t>P=0.0802</t>
+  </si>
+  <si>
+    <t>F (2, 69) = 38.88</t>
+  </si>
+  <si>
+    <t>    Predicted (LS) mean of Jóvenes</t>
+  </si>
+  <si>
+    <t>    Predicted (LS) mean of Adultos</t>
+  </si>
+  <si>
+    <t>-0.09101 to 1.563</t>
+  </si>
+  <si>
+    <t>  Jóvenes</t>
+  </si>
+  <si>
+    <t>    Control vs. SAC</t>
+  </si>
+  <si>
+    <t>0.8966 to 3.738</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>    Control vs. Stevia</t>
+  </si>
+  <si>
+    <t>-4.557 to -0.7714</t>
+  </si>
+  <si>
+    <t>    SAC vs. Stevia</t>
+  </si>
+  <si>
+    <t>-6.891 to -3.072</t>
+  </si>
+  <si>
+    <t>  Adultos</t>
+  </si>
+  <si>
+    <t>-1.663 to 1.179</t>
+  </si>
+  <si>
+    <t>-6.652 to -3.033</t>
+  </si>
+  <si>
+    <t>-6.392 to -2.809</t>
+  </si>
+  <si>
+    <t>Two-way ANOVA , rearing time</t>
+  </si>
+  <si>
+    <t>F (2, 72) = 2.243</t>
+  </si>
+  <si>
+    <t>P=0.1135</t>
+  </si>
+  <si>
+    <t>F (1, 72) = 10.12</t>
+  </si>
+  <si>
+    <t>F (2, 72) = 8.811</t>
+  </si>
+  <si>
+    <t>P=0.0004</t>
+  </si>
+  <si>
+    <t>-20.95 to -4.807</t>
+  </si>
+  <si>
+    <t>1.792 to 29.54</t>
+  </si>
+  <si>
+    <t>    control vs. Stevia</t>
+  </si>
+  <si>
+    <t>6.716 to 43.42</t>
+  </si>
+  <si>
+    <t>-9.593 to 28.40</t>
+  </si>
+  <si>
+    <t>-14.98 to 12.14</t>
+  </si>
+  <si>
+    <t>1.795 to 36.76</t>
+  </si>
+  <si>
+    <t>3.056 to 38.34</t>
+  </si>
+  <si>
+    <t>Two-way ANOVA , entries zone 1</t>
+  </si>
+  <si>
+    <t>F (2, 72) = 2.286</t>
+  </si>
+  <si>
+    <t>P=0.1091</t>
+  </si>
+  <si>
+    <t>F (1, 72) = 6.204</t>
+  </si>
+  <si>
+    <t>P=0.0151</t>
+  </si>
+  <si>
+    <t>F (2, 72) = 4.108</t>
+  </si>
+  <si>
+    <t>P=0.0204</t>
+  </si>
+  <si>
+    <t>0.3023 to 2.726</t>
+  </si>
+  <si>
+    <t>-1.224 to 2.982</t>
+  </si>
+  <si>
+    <t>-3.155 to 2.447</t>
+  </si>
+  <si>
+    <t>-4.060 to 1.593</t>
+  </si>
+  <si>
+    <t>-2.537 to 1.478</t>
+  </si>
+  <si>
+    <t>-6.351 to -1.095</t>
+  </si>
+  <si>
+    <t>-5.821 to -0.5653</t>
+  </si>
+  <si>
+    <t>Two-way ANOVA , total zonas visitadas</t>
+  </si>
+  <si>
+    <t>F (2, 63) = 3.278</t>
+  </si>
+  <si>
+    <t>P=0.0442</t>
+  </si>
+  <si>
+    <t>F (1, 63) = 0.02703</t>
+  </si>
+  <si>
+    <t>P=0.8699</t>
+  </si>
+  <si>
+    <t>F (2, 63) = 37.01</t>
+  </si>
+  <si>
+    <t>-8.413 to 9.921</t>
+  </si>
+  <si>
+    <t>3.039 to 35.20</t>
+  </si>
+  <si>
+    <t>-58.80 to -18.30</t>
+  </si>
+  <si>
+    <t>-78.99 to -36.34</t>
+  </si>
+  <si>
+    <t>-21.80 to 11.05</t>
+  </si>
+  <si>
+    <t>-68.10 to -28.62</t>
+  </si>
+  <si>
+    <t>-62.97 to -22.99</t>
   </si>
 </sst>
 </file>
@@ -2436,6 +2646,2969 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CB63AB-F104-4126-AC52-053A588E3987}">
+  <dimension ref="A1:BC3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6.109</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5.0860000000000003</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3.2930000000000001</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="N2" s="1">
+        <v>2.3109999999999999</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="U2" s="1">
+        <v>3</v>
+      </c>
+      <c r="V2" s="1">
+        <v>4</v>
+      </c>
+      <c r="W2" s="1">
+        <v>4</v>
+      </c>
+      <c r="X2" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>1.0660000000000001</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>1.2829999999999999</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>1.855</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>1.2509999999999999</v>
+      </c>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1">
+        <v>8.2490000000000006</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>4.8849999999999998</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>6.2990000000000004</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>6.0659999999999998</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>6.1340000000000003</v>
+      </c>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+    </row>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2.5950000000000002</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="L3" s="1">
+        <v>5.2679999999999998</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.752</v>
+      </c>
+      <c r="N3" s="1">
+        <v>2.5009999999999999</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1.145</v>
+      </c>
+      <c r="P3" s="1">
+        <v>3.4180000000000001</v>
+      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1">
+        <v>4</v>
+      </c>
+      <c r="U3" s="1">
+        <v>2</v>
+      </c>
+      <c r="V3" s="1">
+        <v>2</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>2.9009999999999998</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>3.6379999999999999</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>3.18</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>2.6960000000000002</v>
+      </c>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1">
+        <v>6.2110000000000003</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>8.4979999999999993</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>6.7069999999999999</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>4.843</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>6.67</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>6.351</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>6.5640000000000001</v>
+      </c>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="T1:AK1"/>
+    <mergeCell ref="AL1:BC1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C10779-313E-47DC-976A-0F15D42663EC}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6.23</v>
+      </c>
+      <c r="C8" s="1">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.9450000000000001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8.0199999999999994E-2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>47.97</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27.51</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>13.76</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>8.5879999999999992</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8.5879999999999992</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>211.8</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>105.9</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>188</v>
+      </c>
+      <c r="C16" s="1">
+        <v>69</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.7240000000000002</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1">
+        <v>441.6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>74</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4.1369999999999996</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3.4009999999999998</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.73609999999999998</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.41460000000000002</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="1">
+        <v>75</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891F677F-E046-4EC7-9102-8419E7303AE6}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-2.6640000000000001</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-4.9820000000000002</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-0.24160000000000001</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-4.8419999999999996</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="1">
+        <v>-4.601</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4.0220000000000002</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.59319999999999995</v>
+      </c>
+      <c r="F24" s="1">
+        <v>16</v>
+      </c>
+      <c r="G24" s="1">
+        <v>15</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5.5250000000000004</v>
+      </c>
+      <c r="I24" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4.0220000000000002</v>
+      </c>
+      <c r="C25" s="1">
+        <v>6.6859999999999999</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-2.6640000000000001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.79010000000000002</v>
+      </c>
+      <c r="F25" s="1">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6</v>
+      </c>
+      <c r="H25" s="1">
+        <v>4.7679999999999998</v>
+      </c>
+      <c r="I25" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="C26" s="1">
+        <v>6.6859999999999999</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-4.9820000000000002</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.79730000000000001</v>
+      </c>
+      <c r="F26" s="1">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1">
+        <v>6</v>
+      </c>
+      <c r="H26" s="1">
+        <v>8.8360000000000003</v>
+      </c>
+      <c r="I26" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1.7070000000000001</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1.948</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-0.24160000000000001</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.59319999999999995</v>
+      </c>
+      <c r="F29" s="1">
+        <v>15</v>
+      </c>
+      <c r="G29" s="1">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.57609999999999995</v>
+      </c>
+      <c r="I29" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1.7070000000000001</v>
+      </c>
+      <c r="C30" s="1">
+        <v>6.5490000000000004</v>
+      </c>
+      <c r="D30" s="1">
+        <v>-4.8419999999999996</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.75549999999999995</v>
+      </c>
+      <c r="F30" s="1">
+        <v>15</v>
+      </c>
+      <c r="G30" s="1">
+        <v>7</v>
+      </c>
+      <c r="H30" s="1">
+        <v>9.0640000000000001</v>
+      </c>
+      <c r="I30" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1.948</v>
+      </c>
+      <c r="C31" s="1">
+        <v>6.5490000000000004</v>
+      </c>
+      <c r="D31" s="1">
+        <v>-4.601</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.748</v>
+      </c>
+      <c r="F31" s="1">
+        <v>16</v>
+      </c>
+      <c r="G31" s="1">
+        <v>7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>8.6989999999999998</v>
+      </c>
+      <c r="I31" s="1">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F6590D-92BD-4645-86F4-029D1FDADF3D}">
+  <dimension ref="A1:BC3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="1">
+        <v>50.3</v>
+      </c>
+      <c r="C2" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>48.5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1">
+        <v>60</v>
+      </c>
+      <c r="G2" s="1">
+        <v>48</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46</v>
+      </c>
+      <c r="I2" s="1">
+        <v>44</v>
+      </c>
+      <c r="J2" s="1">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1">
+        <v>38</v>
+      </c>
+      <c r="L2" s="1">
+        <v>26</v>
+      </c>
+      <c r="M2" s="1">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1">
+        <v>31</v>
+      </c>
+      <c r="O2" s="1">
+        <v>36</v>
+      </c>
+      <c r="P2" s="1">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>36</v>
+      </c>
+      <c r="R2" s="1">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1">
+        <v>24</v>
+      </c>
+      <c r="T2" s="1">
+        <v>6</v>
+      </c>
+      <c r="U2" s="1">
+        <v>35</v>
+      </c>
+      <c r="V2" s="1">
+        <v>12</v>
+      </c>
+      <c r="W2" s="1">
+        <v>16</v>
+      </c>
+      <c r="X2" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>33</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>26</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>13</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>8</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>27</v>
+      </c>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>16.3</v>
+      </c>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+    </row>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="1">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1">
+        <v>44</v>
+      </c>
+      <c r="D3" s="1">
+        <v>68</v>
+      </c>
+      <c r="E3" s="1">
+        <v>61</v>
+      </c>
+      <c r="F3" s="1">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1">
+        <v>93</v>
+      </c>
+      <c r="H3" s="1">
+        <v>42</v>
+      </c>
+      <c r="I3" s="1">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1">
+        <v>54</v>
+      </c>
+      <c r="L3" s="1">
+        <v>20</v>
+      </c>
+      <c r="M3" s="1">
+        <v>49</v>
+      </c>
+      <c r="N3" s="1">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1">
+        <v>17</v>
+      </c>
+      <c r="P3" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>38</v>
+      </c>
+      <c r="R3" s="1">
+        <v>45</v>
+      </c>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1">
+        <v>69</v>
+      </c>
+      <c r="U3" s="1">
+        <v>66</v>
+      </c>
+      <c r="V3" s="1">
+        <v>43</v>
+      </c>
+      <c r="W3" s="1">
+        <v>54</v>
+      </c>
+      <c r="X3" s="1">
+        <v>86</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>60</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>14</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>43</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>7</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>47</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>20</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>33</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>38</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>67</v>
+      </c>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>33</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>29.2</v>
+      </c>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="T1:AK1"/>
+    <mergeCell ref="AL1:BC1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A1FB4B-C3A2-4E8B-BB47-F9CC0959E440}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4.2590000000000003</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.1135</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>9.6039999999999992</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>16.73</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1187</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>593.5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2677</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2677</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4663</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2331</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>19051</v>
+      </c>
+      <c r="C16" s="1">
+        <v>72</v>
+      </c>
+      <c r="D16" s="1">
+        <v>264.60000000000002</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1">
+        <v>27869</v>
+      </c>
+      <c r="C17" s="1">
+        <v>77</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="1">
+        <v>22.87</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="1">
+        <v>35.75</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1">
+        <v>-12.88</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4.05</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="1">
+        <v>78</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3139E4B3-9216-4AA5-ADF1-12CC64A1A8A8}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="1">
+        <v>15.66</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25.07</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="1">
+        <v>9.4019999999999992</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-1.419</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="1">
+        <v>19.28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1">
+        <v>36.450000000000003</v>
+      </c>
+      <c r="C24" s="1">
+        <v>20.79</v>
+      </c>
+      <c r="D24" s="1">
+        <v>15.66</v>
+      </c>
+      <c r="E24" s="1">
+        <v>5.7969999999999997</v>
+      </c>
+      <c r="F24" s="1">
+        <v>18</v>
+      </c>
+      <c r="G24" s="1">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3.8220000000000001</v>
+      </c>
+      <c r="I24" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="1">
+        <v>36.450000000000003</v>
+      </c>
+      <c r="C25" s="1">
+        <v>11.38</v>
+      </c>
+      <c r="D25" s="1">
+        <v>25.07</v>
+      </c>
+      <c r="E25" s="1">
+        <v>7.6680000000000001</v>
+      </c>
+      <c r="F25" s="1">
+        <v>18</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6</v>
+      </c>
+      <c r="H25" s="1">
+        <v>4.6230000000000002</v>
+      </c>
+      <c r="I25" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="1">
+        <v>20.79</v>
+      </c>
+      <c r="C26" s="1">
+        <v>11.38</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9.4019999999999992</v>
+      </c>
+      <c r="E26" s="1">
+        <v>7.9370000000000003</v>
+      </c>
+      <c r="F26" s="1">
+        <v>14</v>
+      </c>
+      <c r="G26" s="1">
+        <v>6</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1.675</v>
+      </c>
+      <c r="I26" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1">
+        <v>41.71</v>
+      </c>
+      <c r="C29" s="1">
+        <v>43.13</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-1.419</v>
+      </c>
+      <c r="E29" s="1">
+        <v>5.6660000000000004</v>
+      </c>
+      <c r="F29" s="1">
+        <v>17</v>
+      </c>
+      <c r="G29" s="1">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.35420000000000001</v>
+      </c>
+      <c r="I29" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="1">
+        <v>41.71</v>
+      </c>
+      <c r="C30" s="1">
+        <v>22.43</v>
+      </c>
+      <c r="D30" s="1">
+        <v>19.28</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="F30" s="1">
+        <v>17</v>
+      </c>
+      <c r="G30" s="1">
+        <v>7</v>
+      </c>
+      <c r="H30" s="1">
+        <v>3.7320000000000002</v>
+      </c>
+      <c r="I30" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="1">
+        <v>43.13</v>
+      </c>
+      <c r="C31" s="1">
+        <v>22.43</v>
+      </c>
+      <c r="D31" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="E31" s="1">
+        <v>7.3710000000000004</v>
+      </c>
+      <c r="F31" s="1">
+        <v>16</v>
+      </c>
+      <c r="G31" s="1">
+        <v>7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3.9710000000000001</v>
+      </c>
+      <c r="I31" s="1">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E13C0BD-DCB6-4B77-A829-B855A73750CB}">
+  <dimension ref="A1:AZ3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>2</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>11</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1</v>
+      </c>
+      <c r="T2" s="1">
+        <v>3</v>
+      </c>
+      <c r="U2" s="1">
+        <v>5</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2</v>
+      </c>
+      <c r="W2" s="1">
+        <v>6</v>
+      </c>
+      <c r="X2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>2</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>12</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>2</v>
+      </c>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>5</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>4</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>3</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>3</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>8</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>7</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>7</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:R1"/>
+    <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="AJ1:AZ1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB1F5A7-F9FF-421F-8AC5-A36221314D3D}">
   <dimension ref="A1:F29"/>
@@ -2822,6 +5995,2253 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF25453C-6FA1-4DBD-897E-79D557EBC402}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4.6680000000000001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.1091</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6.3360000000000003</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8.391</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27.33</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>13.67</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>49.13</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>24.56</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>430.5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>72</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5.9790000000000001</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1">
+        <v>585.5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>77</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3.6379999999999999</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2.1230000000000002</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1.514</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="1">
+        <v>78</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{863277EF-4730-4069-9290-734237D9DF15}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.87919999999999998</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-0.35420000000000001</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-1.2330000000000001</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-0.52939999999999998</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-3.7229999999999999</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="1">
+        <v>-3.1930000000000001</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3.8130000000000002</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.87919999999999998</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.87880000000000003</v>
+      </c>
+      <c r="F24" s="1">
+        <v>16</v>
+      </c>
+      <c r="G24" s="1">
+        <v>15</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1.415</v>
+      </c>
+      <c r="I24" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3.8130000000000002</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-0.35420000000000001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1.171</v>
+      </c>
+      <c r="F25" s="1">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.4279</v>
+      </c>
+      <c r="I25" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-1.2330000000000001</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1.181</v>
+      </c>
+      <c r="F26" s="1">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1">
+        <v>6</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1.4770000000000001</v>
+      </c>
+      <c r="I26" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.70589999999999997</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-0.52939999999999998</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.8387</v>
+      </c>
+      <c r="F29" s="1">
+        <v>17</v>
+      </c>
+      <c r="G29" s="1">
+        <v>17</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.89270000000000005</v>
+      </c>
+      <c r="I29" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.70589999999999997</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.4290000000000003</v>
+      </c>
+      <c r="D30" s="1">
+        <v>-3.7229999999999999</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="F30" s="1">
+        <v>17</v>
+      </c>
+      <c r="G30" s="1">
+        <v>7</v>
+      </c>
+      <c r="H30" s="1">
+        <v>4.7939999999999996</v>
+      </c>
+      <c r="I30" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="C31" s="1">
+        <v>4.4290000000000003</v>
+      </c>
+      <c r="D31" s="1">
+        <v>-3.1930000000000001</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="F31" s="1">
+        <v>17</v>
+      </c>
+      <c r="G31" s="1">
+        <v>7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>4.1120000000000001</v>
+      </c>
+      <c r="I31" s="1">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E17648-3D83-427D-8E0C-4B028AA6B44C}">
+  <dimension ref="A1:AZ3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>48</v>
+      </c>
+      <c r="D2" s="1">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1">
+        <v>39</v>
+      </c>
+      <c r="G2" s="1">
+        <v>36</v>
+      </c>
+      <c r="H2" s="1">
+        <v>75</v>
+      </c>
+      <c r="I2" s="1">
+        <v>78</v>
+      </c>
+      <c r="J2" s="1">
+        <v>90</v>
+      </c>
+      <c r="K2" s="1">
+        <v>52</v>
+      </c>
+      <c r="L2" s="1">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1">
+        <v>21</v>
+      </c>
+      <c r="O2" s="1">
+        <v>21</v>
+      </c>
+      <c r="P2" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>11</v>
+      </c>
+      <c r="R2" s="1">
+        <v>15</v>
+      </c>
+      <c r="S2" s="1">
+        <v>11</v>
+      </c>
+      <c r="T2" s="1">
+        <v>40</v>
+      </c>
+      <c r="U2" s="1">
+        <v>47</v>
+      </c>
+      <c r="V2" s="1">
+        <v>26</v>
+      </c>
+      <c r="W2" s="1">
+        <v>24</v>
+      </c>
+      <c r="X2" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>16</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>12</v>
+      </c>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1">
+        <v>95</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>79</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>86</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>64</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>71</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>59</v>
+      </c>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1">
+        <v>56</v>
+      </c>
+      <c r="I3" s="1">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1">
+        <v>54</v>
+      </c>
+      <c r="L3" s="1">
+        <v>8</v>
+      </c>
+      <c r="M3" s="1">
+        <v>34</v>
+      </c>
+      <c r="N3" s="1">
+        <v>19</v>
+      </c>
+      <c r="O3" s="1">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1">
+        <v>56</v>
+      </c>
+      <c r="T3" s="1">
+        <v>42</v>
+      </c>
+      <c r="U3" s="1">
+        <v>40</v>
+      </c>
+      <c r="V3" s="1">
+        <v>13</v>
+      </c>
+      <c r="W3" s="1">
+        <v>32</v>
+      </c>
+      <c r="X3" s="1">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>21</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>14</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>16</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>50</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>46</v>
+      </c>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1">
+        <v>51</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>66</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>81</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>67</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>65</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>103</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>80</v>
+      </c>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:R1"/>
+    <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="AJ1:AZ1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFFC1178-298C-4F27-8BFA-5DA37CA1A612}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.8939999999999999E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.86990000000000001</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>51.88</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2069</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1035</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>23360</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>11680</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>19884</v>
+      </c>
+      <c r="C16" s="1">
+        <v>63</v>
+      </c>
+      <c r="D16" s="1">
+        <v>315.60000000000002</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1">
+        <v>45026</v>
+      </c>
+      <c r="C17" s="1">
+        <v>68</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="1">
+        <v>43.59</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="1">
+        <v>42.84</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.75409999999999999</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4.5869999999999997</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="1">
+        <v>69</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99CBCE90-C1E6-491C-A26D-FC2B838AFD03}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="1">
+        <v>19.12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-38.549999999999997</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-57.67</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-5.3789999999999996</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-48.36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="1">
+        <v>-42.98</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="1">
+        <v>37.119999999999997</v>
+      </c>
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>19.12</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6.6980000000000004</v>
+      </c>
+      <c r="F24" s="1">
+        <v>17</v>
+      </c>
+      <c r="G24" s="1">
+        <v>12</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4.0359999999999996</v>
+      </c>
+      <c r="I24" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="1">
+        <v>37.119999999999997</v>
+      </c>
+      <c r="C25" s="1">
+        <v>75.67</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-38.549999999999997</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8.4359999999999999</v>
+      </c>
+      <c r="F25" s="1">
+        <v>17</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6</v>
+      </c>
+      <c r="H25" s="1">
+        <v>6.4619999999999997</v>
+      </c>
+      <c r="I25" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="1">
+        <v>18</v>
+      </c>
+      <c r="C26" s="1">
+        <v>75.67</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-57.67</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8.8829999999999991</v>
+      </c>
+      <c r="F26" s="1">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1">
+        <v>6</v>
+      </c>
+      <c r="H26" s="1">
+        <v>9.1809999999999992</v>
+      </c>
+      <c r="I26" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="1">
+        <v>24.93</v>
+      </c>
+      <c r="C29" s="1">
+        <v>30.31</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-5.3789999999999996</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6.843</v>
+      </c>
+      <c r="F29" s="1">
+        <v>14</v>
+      </c>
+      <c r="G29" s="1">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="I29" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="1">
+        <v>24.93</v>
+      </c>
+      <c r="C30" s="1">
+        <v>73.290000000000006</v>
+      </c>
+      <c r="D30" s="1">
+        <v>-48.36</v>
+      </c>
+      <c r="E30" s="1">
+        <v>8.2240000000000002</v>
+      </c>
+      <c r="F30" s="1">
+        <v>14</v>
+      </c>
+      <c r="G30" s="1">
+        <v>7</v>
+      </c>
+      <c r="H30" s="1">
+        <v>8.3160000000000007</v>
+      </c>
+      <c r="I30" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="1">
+        <v>30.31</v>
+      </c>
+      <c r="C31" s="1">
+        <v>73.290000000000006</v>
+      </c>
+      <c r="D31" s="1">
+        <v>-42.98</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8.3290000000000006</v>
+      </c>
+      <c r="F31" s="1">
+        <v>13</v>
+      </c>
+      <c r="G31" s="1">
+        <v>7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>7.298</v>
+      </c>
+      <c r="I31" s="1">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
